--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484348_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484348_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1665</v>
+        <v>4.6019</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3132</v>
+        <v>2.021</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8533</v>
+        <v>2.5809</v>
       </c>
       <c r="G2" t="n">
         <v>1.6493</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3218</v>
+        <v>0.7573</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6657</v>
+        <v>0.0421</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9876</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.2186</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5571</v>
+        <v>2.4426</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8843</v>
+        <v>1.7426</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6728</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
         <v>1.717</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1805</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2943</v>
+        <v>-0.436</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4748</v>
+        <v>0.502</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2072</v>
+        <v>2.2465</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0319</v>
+        <v>1.1529</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1753</v>
+        <v>1.0936</v>
       </c>
       <c r="G4" t="n">
         <v>2.0158</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3597</v>
+        <v>1.399</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8173</v>
+        <v>0.9383</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5424</v>
+        <v>0.4607</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3869</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0741</v>
+        <v>2.1152</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3614</v>
+        <v>1.3208</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7127</v>
+        <v>0.7944</v>
       </c>
       <c r="G5" t="n">
         <v>1.5279</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.082</v>
+        <v>0.1231</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2337</v>
+        <v>-0.2743</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3158</v>
+        <v>0.3975</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1219</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3805</v>
+        <v>1.6632</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.9435</v>
       </c>
       <c r="F6" t="n">
         <v>0.7198</v>
@@ -922,10 +922,10 @@
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0881</v>
+        <v>0.3708</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4621</v>
+        <v>-0.1794</v>
       </c>
       <c r="U6" t="n">
         <v>0.5501</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4611</v>
+        <v>0.6304</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2857</v>
+        <v>0.1225</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7468</v>
+        <v>0.5079</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0529</v>
+        <v>0.5258</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2456</v>
+        <v>2.3331</v>
       </c>
       <c r="I7" t="n">
         <v>-1.8073</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2238</v>
+        <v>1.0901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0435</v>
+        <v>3.0315</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2673</v>
+        <v>-1.9414</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.5643</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2891</v>
+        <v>-0.6984</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5401</v>
+        <v>0.134</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.514</v>
+        <v>0.4684</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6962</v>
+        <v>0.0091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1822</v>
+        <v>0.4593</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>-1.3405</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2796</v>
+        <v>0.3419</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1591</v>
+        <v>-1.2602</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4387</v>
+        <v>1.6021</v>
       </c>
       <c r="G8" t="n">
         <v>0.0378</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5739</v>
+        <v>0.6362</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3715</v>
+        <v>0.2704</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2024</v>
+        <v>0.3658</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3321</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1148</v>
+        <v>0.2284</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2414</v>
+        <v>-0.8724</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1266</v>
+        <v>1.1008</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5258</v>
+        <v>-2.0529</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3331</v>
+        <v>-0.2456</v>
       </c>
       <c r="I9" t="n">
         <v>-1.8073</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0901</v>
+        <v>-1.2238</v>
       </c>
       <c r="K9" t="n">
-        <v>3.0315</v>
+        <v>0.0435</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9414</v>
+        <v>-1.2673</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5643</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6984</v>
+        <v>-0.2891</v>
       </c>
       <c r="O9" t="n">
-        <v>0.134</v>
+        <v>-0.5401</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2767</v>
+        <v>0.2813</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3548</v>
+        <v>0.1095</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0781</v>
+        <v>0.1719</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3405</v>
+        <v>1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3907</v>
+        <v>-0.0425</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6412</v>
+        <v>-1.0751</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2504</v>
+        <v>1.0326</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0674</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2041</v>
+        <v>0.5523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2888</v>
+        <v>0.2773</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4929</v>
+        <v>0.2751</v>
       </c>
       <c r="V10" t="n">
         <v>0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4715</v>
+        <v>-0.9265</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8887</v>
+        <v>-2.2621</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4172</v>
+        <v>1.3355</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1241</v>
@@ -1312,13 +1312,13 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3241</v>
+        <v>0.2208</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5309</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2068</v>
+        <v>0.1251</v>
       </c>
       <c r="V11" t="n">
         <v>0.6093</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1559</v>
+        <v>-3.4001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8823</v>
+        <v>-4.7724</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7264</v>
+        <v>1.3723</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3197</v>
@@ -1390,13 +1390,13 @@
         <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9032</v>
+        <v>1.6591</v>
       </c>
       <c r="T12" t="n">
-        <v>1.607</v>
+        <v>0.7169</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2962</v>
+        <v>0.9422</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3953</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.993199999999998</v>
+        <v>9.900999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8468</v>
+        <v>-2.938900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12.84</v>
+        <v>12.8399</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9300999999999999</v>
+        <v>-0.9301000000000008</v>
       </c>
       <c r="H13" t="n">
         <v>9.185300000000002</v>
@@ -1468,10 +1468,10 @@
         <v>19.5343</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6265</v>
+        <v>6.5344</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6617</v>
+        <v>1.5696</v>
       </c>
       <c r="U13" t="n">
         <v>4.9649</v>
@@ -1480,7 +1480,7 @@
         <v>0.3897999999999997</v>
       </c>
       <c r="W13" t="n">
-        <v>5.431799999999999</v>
+        <v>5.431799999999998</v>
       </c>
       <c r="X13" t="n">
         <v>-5.042</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0558</v>
+        <v>2.3388</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8371</v>
+        <v>-1.4438</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8929</v>
+        <v>3.7826</v>
       </c>
       <c r="G14" t="n">
         <v>2.1628</v>
@@ -1546,13 +1546,13 @@
         <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5023</v>
+        <v>-0.2146</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1791</v>
+        <v>-0.4276</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3233</v>
+        <v>0.213</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9821</v>
+        <v>2.1922</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4427</v>
+        <v>1.5438</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5395</v>
+        <v>0.6484</v>
       </c>
       <c r="G15" t="n">
         <v>2.3142</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7693</v>
+        <v>-0.5592</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0013</v>
+        <v>-0.9002</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2321</v>
+        <v>0.341</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3686</v>
+        <v>0.6332</v>
       </c>
       <c r="E16" t="n">
-        <v>3.308</v>
+        <v>3.4091</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9394</v>
+        <v>-2.776</v>
       </c>
       <c r="G16" t="n">
         <v>3.0699</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3657</v>
+        <v>-1.1012</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6244</v>
+        <v>-0.5233</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7413</v>
+        <v>-0.5779</v>
       </c>
       <c r="V16" t="n">
         <v>-2.7029</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3176</v>
+        <v>-0.2512</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4949</v>
+        <v>-2.3265</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1773</v>
+        <v>2.0754</v>
       </c>
       <c r="G17" t="n">
-        <v>0.516</v>
+        <v>0.6364</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6836</v>
+        <v>-0.065</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1996</v>
+        <v>0.7013</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2943</v>
+        <v>0.0519</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1729</v>
+        <v>0.0243</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>0.0276</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7783</v>
+        <v>0.5844</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8565</v>
+        <v>-0.0893</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0782</v>
+        <v>0.6737</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7348</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.4929</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1029</v>
+        <v>-0.4615</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4015</v>
+        <v>-0.1395</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2986</v>
+        <v>-0.322</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0041</v>
+        <v>0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1052</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1011</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6559</v>
+        <v>-0.4589</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6741</v>
+        <v>-1.7983</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0182</v>
+        <v>1.3394</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6741</v>
+        <v>0.516</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.6836</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6741</v>
+        <v>1.1996</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6741</v>
+        <v>1.2943</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.1729</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.7783</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.8565</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.0782</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.4929</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0182</v>
+        <v>-0.2442</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.7049</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0182</v>
+        <v>0.4607</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.0041</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1011</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>À. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6662</v>
+        <v>-0.6287</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2254</v>
+        <v>-0.6741</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5592</v>
+        <v>0.0454</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6364</v>
+        <v>-0.6741</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.065</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7013</v>
+        <v>-0.6741</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0519</v>
+        <v>-0.6741</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0276</v>
+        <v>-0.6741</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5844</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0893</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6737</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0.0454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8381</v>
+        <v>0.0454</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8365</v>
+        <v>-1.3983</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1353</v>
+        <v>-1.8319</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2988</v>
+        <v>0.4336</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2936</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7814</v>
+        <v>-0.3432</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9684</v>
+        <v>-0.665</v>
       </c>
       <c r="U20" t="n">
-        <v>0.187</v>
+        <v>0.3218</v>
       </c>
       <c r="V20" t="n">
         <v>0.0664</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7518</v>
+        <v>-2.6779</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7848</v>
+        <v>-1.6837</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.967</v>
+        <v>-0.9942</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8452</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2845</v>
+        <v>0.2572</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0237</v>
+        <v>-3.1132</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4211</v>
+        <v>-2.32</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6026</v>
+        <v>-0.7932</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2771</v>
@@ -2170,13 +2170,13 @@
         <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9498</v>
+        <v>-1.0393</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5777</v>
+        <v>-0.4766</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3721</v>
+        <v>-0.5628</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2108</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.148</v>
+        <v>-4.9549</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6272</v>
+        <v>-6.3238</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4792</v>
+        <v>1.3689</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6791</v>
@@ -2248,13 +2248,13 @@
         <v>2.5395</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2228</v>
+        <v>-1.0297</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1691</v>
+        <v>-0.8658</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0536</v>
+        <v>-0.1639</v>
       </c>
       <c r="V23" t="n">
         <v>-0.488</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.993199999999998</v>
+        <v>-8.318899999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-13.4492</v>
       </c>
       <c r="F24" t="n">
-        <v>4.456100000000001</v>
+        <v>5.1303</v>
       </c>
       <c r="G24" t="n">
         <v>0.930200000000001</v>
@@ -2305,7 +2305,7 @@
         <v>3.913899999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>2.7033</v>
+        <v>2.703300000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-5.687</v>
@@ -2314,7 +2314,7 @@
         <v>-13.0994</v>
       </c>
       <c r="O24" t="n">
-        <v>7.412199999999999</v>
+        <v>7.4122</v>
       </c>
       <c r="P24" t="n">
         <v>-3.9068</v>
@@ -2326,19 +2326,19 @@
         <v>15.6273</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.6266</v>
+        <v>-4.9523</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.9648</v>
+        <v>-4.9649</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6613999999999999</v>
+        <v>0.01250000000000012</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3897999999999998</v>
       </c>
       <c r="W24" t="n">
-        <v>4.4327</v>
+        <v>4.432700000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-4.8225</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484348_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484348_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,28 +570,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6019</v>
+        <v>3.9879</v>
       </c>
       <c r="E2" t="n">
-        <v>2.021</v>
+        <v>1.407</v>
       </c>
       <c r="F2" t="n">
         <v>2.5809</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6493</v>
+        <v>1.0353</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6882</v>
+        <v>2.0742</v>
       </c>
       <c r="I2" t="n">
         <v>-1.0389</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0691</v>
+        <v>1.4551</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7027</v>
+        <v>2.0888</v>
       </c>
       <c r="L2" t="n">
         <v>-0.6336000000000001</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0.3321</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.5423</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>G. SABATÉS SALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3419</v>
+        <v>0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2602</v>
+        <v>0.614</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6021</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0378</v>
+        <v>0.614</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8852</v>
+        <v>0.614</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8474</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2218</v>
+        <v>0.614</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7601</v>
+        <v>0.614</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9818</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2595</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1251</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1344</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6362</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2704</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3658</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2284</v>
+        <v>0.3419</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8724</v>
+        <v>-1.2602</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1008</v>
+        <v>1.6021</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0529</v>
+        <v>0.0378</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2456</v>
+        <v>1.8852</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8073</v>
+        <v>-1.8474</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2238</v>
+        <v>-0.2218</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0435</v>
+        <v>1.7601</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2673</v>
+        <v>-1.9818</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8290999999999999</v>
+        <v>0.2595</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2891</v>
+        <v>0.1251</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5401</v>
+        <v>0.1344</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2813</v>
+        <v>0.6362</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1095</v>
+        <v>0.2704</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1719</v>
+        <v>0.3658</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0425</v>
+        <v>0.2284</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0751</v>
+        <v>-0.8724</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0326</v>
+        <v>1.1008</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0674</v>
+        <v>-2.0529</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.703</v>
+        <v>-0.2456</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3644</v>
+        <v>-1.8073</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6528</v>
+        <v>-1.2238</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6933</v>
+        <v>0.0435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-1.2673</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4146</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0097</v>
+        <v>-0.2891</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4049</v>
+        <v>-0.5401</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5523</v>
+        <v>0.2813</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2773</v>
+        <v>0.1095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2751</v>
+        <v>0.1719</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9265</v>
+        <v>-0.0425</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2621</v>
+        <v>-1.0751</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3355</v>
+        <v>1.0326</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1241</v>
+        <v>-1.0674</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1016</v>
+        <v>-0.703</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0225</v>
+        <v>-0.3644</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.635</v>
+        <v>-0.6528</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6127</v>
+        <v>-0.6933</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0223</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4891</v>
+        <v>-0.4146</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4889</v>
+        <v>-0.0097</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0002</v>
+        <v>-0.4049</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2208</v>
+        <v>0.5523</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.2773</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1251</v>
+        <v>0.2751</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
         <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4001</v>
+        <v>-0.9265</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7724</v>
+        <v>-2.2621</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3723</v>
+        <v>1.3355</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3197</v>
+        <v>-3.1241</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5889</v>
+        <v>-1.1016</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2692</v>
+        <v>-2.0225</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1602</v>
+        <v>-2.635</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1602</v>
+        <v>-0.6127</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-2.0223</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1595</v>
+        <v>-0.4891</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4287</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2692</v>
+        <v>-0.0002</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3441</v>
+        <v>1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6591</v>
+        <v>0.2208</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7169</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9422</v>
+        <v>0.1251</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3953</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.9498</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.900999999999998</v>
+        <v>-3.4001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.938900000000001</v>
+        <v>-4.7724</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8399</v>
+        <v>1.3723</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9301000000000008</v>
+        <v>-1.3197</v>
       </c>
       <c r="H13" t="n">
-        <v>9.185300000000002</v>
+        <v>-1.5889</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.1154</v>
+        <v>0.2692</v>
       </c>
       <c r="J13" t="n">
-        <v>5.687100000000003</v>
+        <v>-1.1602</v>
       </c>
       <c r="K13" t="n">
-        <v>13.0993</v>
+        <v>-1.1602</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.412100000000001</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6172</v>
+        <v>-0.1595</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.9141</v>
+        <v>-0.4287</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.7035</v>
+        <v>0.2692</v>
       </c>
       <c r="P13" t="n">
-        <v>3.9068</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6273</v>
+        <v>-4.8836</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5343</v>
+        <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>6.5344</v>
+        <v>1.6591</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5696</v>
+        <v>0.7169</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9649</v>
+        <v>0.9422</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3897999999999997</v>
+        <v>-1.3953</v>
       </c>
       <c r="W13" t="n">
-        <v>5.431799999999998</v>
+        <v>0.5545</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.042</v>
+        <v>-1.9498</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3388</v>
+        <v>9.901000000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4438</v>
+        <v>-2.938899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7826</v>
+        <v>12.8399</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1628</v>
+        <v>-0.9300999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1673</v>
+        <v>9.185300000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9955</v>
+        <v>-10.1154</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5232</v>
+        <v>5.687099999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7406</v>
+        <v>13.0994</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7827</v>
+        <v>-7.412100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6395</v>
+        <v>-6.6172</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5733</v>
+        <v>-3.9141</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2128</v>
+        <v>-2.7035</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>3.9068</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5395</v>
+        <v>-15.6273</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>19.5343</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2146</v>
+        <v>6.5344</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4276</v>
+        <v>1.5696</v>
       </c>
       <c r="U14" t="n">
-        <v>0.213</v>
+        <v>4.9649</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3897999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>5.431799999999998</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.042</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1922</v>
+        <v>2.3388</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5438</v>
+        <v>-1.4438</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6484</v>
+        <v>3.7826</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3142</v>
+        <v>2.1628</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3556</v>
+        <v>0.1673</v>
       </c>
       <c r="I15" t="n">
-        <v>3.6697</v>
+        <v>1.9955</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2923</v>
+        <v>1.5232</v>
       </c>
       <c r="K15" t="n">
-        <v>0.431</v>
+        <v>0.7406</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8612</v>
+        <v>0.7827</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9781</v>
+        <v>0.6395</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7866</v>
+        <v>-0.5733</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8085</v>
+        <v>1.2128</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3441</v>
+        <v>-2.5395</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5592</v>
+        <v>-0.2146</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9002</v>
+        <v>-0.4276</v>
       </c>
       <c r="U15" t="n">
-        <v>0.341</v>
+        <v>0.213</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6332</v>
+        <v>2.1922</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4091</v>
+        <v>1.5438</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.776</v>
+        <v>0.6484</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0699</v>
+        <v>2.3142</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5999</v>
+        <v>-1.3556</v>
       </c>
       <c r="I16" t="n">
-        <v>1.47</v>
+        <v>3.6697</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1826</v>
+        <v>3.2923</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5214</v>
+        <v>0.431</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6613</v>
+        <v>2.8612</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1127</v>
+        <v>-0.9781</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.9215</v>
+        <v>-1.7866</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8087</v>
+        <v>0.8085</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R16" t="n">
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1012</v>
+        <v>-0.5592</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5233</v>
+        <v>-0.9002</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5779</v>
+        <v>0.341</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7029</v>
+        <v>1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6481</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2512</v>
+        <v>0.6332</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3265</v>
+        <v>3.4091</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0754</v>
+        <v>-2.776</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6364</v>
+        <v>3.0699</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.065</v>
+        <v>1.5999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7013</v>
+        <v>1.47</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0519</v>
+        <v>4.1826</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0243</v>
+        <v>3.5214</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0276</v>
+        <v>0.6613</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5844</v>
+        <v>-1.1127</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0893</v>
+        <v>-1.9215</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6737</v>
+        <v>0.8087</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3674</v>
+        <v>1.3674</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4615</v>
+        <v>-1.1012</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1395</v>
+        <v>-0.5233</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.322</v>
+        <v>-0.5779</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>-2.7029</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8865</v>
+        <v>-0.0549</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0549</v>
+        <v>-2.6481</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4589</v>
+        <v>-0.2512</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7983</v>
+        <v>-2.3265</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3394</v>
+        <v>2.0754</v>
       </c>
       <c r="G18" t="n">
-        <v>0.516</v>
+        <v>0.6364</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6836</v>
+        <v>-0.065</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1996</v>
+        <v>0.7013</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2943</v>
+        <v>0.0519</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1729</v>
+        <v>0.0243</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1214</v>
+        <v>0.0276</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7783</v>
+        <v>0.5844</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8565</v>
+        <v>-0.0893</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0782</v>
+        <v>0.6737</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.7348</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.4929</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
         <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2442</v>
+        <v>-0.4615</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7049</v>
+        <v>-0.1395</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4607</v>
+        <v>-0.322</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0041</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1052</v>
+        <v>0.8865</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1011</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>À. ANTEQUERA SOLER</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6287</v>
+        <v>-0.4589</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6741</v>
+        <v>-1.7983</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0454</v>
+        <v>1.3394</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6741</v>
+        <v>0.516</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.6836</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6741</v>
+        <v>1.1996</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6741</v>
+        <v>1.2943</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.1729</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6741</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.7783</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.8565</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.0782</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.4929</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0454</v>
+        <v>-0.2442</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.7049</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0454</v>
+        <v>0.4607</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.0041</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1052</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1011</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>A. ANTEQUERA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3983</v>
+        <v>-0.6287</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8319</v>
+        <v>-0.6741</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4336</v>
+        <v>0.0454</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2936</v>
+        <v>-0.6741</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5518</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7418</v>
+        <v>-0.6741</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7762</v>
+        <v>-0.6741</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3697</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1459</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5174</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9215</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3432</v>
+        <v>0.0454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.665</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3218</v>
+        <v>0.0454</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0664</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0664</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6779</v>
+        <v>-1.3983</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6837</v>
+        <v>-1.8319</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9942</v>
+        <v>0.4336</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8452</v>
+        <v>-2.2936</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6565</v>
+        <v>-1.5518</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1887</v>
+        <v>-0.7418</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2263</v>
+        <v>-0.7762</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6332</v>
+        <v>0.3697</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-1.1459</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6188</v>
+        <v>-1.5174</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0233</v>
+        <v>-1.9215</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4045</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0048</v>
+        <v>-0.3432</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.262</v>
+        <v>-0.665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2572</v>
+        <v>0.3218</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>0.0664</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0.0664</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1132</v>
+        <v>-2.6779</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.32</v>
+        <v>-1.6837</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7932</v>
+        <v>-0.9942</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2771</v>
+        <v>-1.8452</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8821</v>
+        <v>-1.6565</v>
       </c>
       <c r="I22" t="n">
-        <v>1.605</v>
+        <v>-0.1887</v>
       </c>
       <c r="J22" t="n">
-        <v>0.11</v>
+        <v>-1.2263</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5513</v>
+        <v>-0.6332</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6613</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.387</v>
+        <v>-0.6188</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3308</v>
+        <v>-1.0233</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9437</v>
+        <v>0.4045</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0393</v>
+        <v>-0.0048</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4766</v>
+        <v>-0.262</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5628</v>
+        <v>0.2572</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2108</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2108</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9549</v>
+        <v>-3.1132</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.3238</v>
+        <v>-2.32</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3689</v>
+        <v>-0.7932</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6791</v>
+        <v>-1.2771</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.758</v>
+        <v>-2.8821</v>
       </c>
       <c r="I23" t="n">
-        <v>1.079</v>
+        <v>1.605</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1605</v>
+        <v>0.11</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.1615</v>
+        <v>-0.5513</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001</v>
+        <v>0.6613</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-1.387</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5966</v>
+        <v>-2.3308</v>
       </c>
       <c r="O23" t="n">
-        <v>1.078</v>
+        <v>0.9437</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.2975</v>
+        <v>-1.9534</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0297</v>
+        <v>-1.0393</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8658</v>
+        <v>-0.4766</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1639</v>
+        <v>-0.5628</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.488</v>
+        <v>-0.2108</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.488</v>
+        <v>-0.2108</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,152 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-4.9549</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-6.3238</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3689</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.6791</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.758</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.1605</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.1615</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.5185999999999999</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.5966</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-4.2975</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.5395</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.0297</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.8658</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1639</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.488</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.488</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484348_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>-8.318899999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>-13.4492</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>5.1303</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G25" t="n">
         <v>0.930200000000001</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H25" t="n">
         <v>-9.185400000000001</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>10.1155</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>6.617200000000001</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>3.913899999999999</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>2.703300000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>-5.687</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N25" t="n">
         <v>-13.0994</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O25" t="n">
         <v>7.4122</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P25" t="n">
         <v>-3.9068</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q25" t="n">
         <v>-19.5342</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>-4.9523</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>-4.9649</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>0.01250000000000012</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V25" t="n">
         <v>-0.3897999999999998</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W25" t="n">
         <v>4.432700000000001</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>-4.8225</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
